--- a/data_raw/FASTRESS_measures-food.xlsx
+++ b/data_raw/FASTRESS_measures-food.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh.sharepoint.com/sites/FASTress963/Shared Documents/General/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11754330-15BC-41F4-9735-1FB6643AC49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6641EC98-8404-4259-A361-9B0FDF5DD218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="79">
   <si>
     <t>FASTRESS-ID</t>
   </si>
@@ -295,6 +295,15 @@
   </si>
   <si>
     <t>sub-049</t>
+  </si>
+  <si>
+    <t>sub-010</t>
+  </si>
+  <si>
+    <t>sub-012</t>
+  </si>
+  <si>
+    <t>sub-087</t>
   </si>
   <si>
     <t>Apple pieces were not counted but 3/4 of an apple was administered with an equivalent of 120g. It was estimated that 2 pieces were eaten between pre and post</t>
@@ -4793,105 +4802,291 @@
       <c r="AF41" s="4"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="3"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="12"/>
-      <c r="P42" s="12"/>
-      <c r="Q42" s="12"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
-      <c r="T42" s="13"/>
-      <c r="U42" s="13"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="13"/>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="13"/>
-      <c r="Z42" s="15"/>
-      <c r="AA42" s="15"/>
-      <c r="AB42" s="15"/>
-      <c r="AC42" s="15"/>
-      <c r="AD42" s="15"/>
-      <c r="AE42" s="15"/>
+      <c r="A42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="12">
+        <v>118</v>
+      </c>
+      <c r="C42" s="12">
+        <v>24</v>
+      </c>
+      <c r="D42" s="12">
+        <v>47</v>
+      </c>
+      <c r="E42" s="12">
+        <v>6</v>
+      </c>
+      <c r="F42" s="12">
+        <v>30</v>
+      </c>
+      <c r="G42" s="12">
+        <v>6</v>
+      </c>
+      <c r="H42" s="13">
+        <v>34</v>
+      </c>
+      <c r="I42" s="13">
+        <v>12</v>
+      </c>
+      <c r="J42" s="13">
+        <v>19</v>
+      </c>
+      <c r="K42" s="13">
+        <v>4</v>
+      </c>
+      <c r="L42" s="13">
+        <v>33</v>
+      </c>
+      <c r="M42" s="13">
+        <v>13</v>
+      </c>
+      <c r="N42" s="12">
+        <v>33</v>
+      </c>
+      <c r="O42" s="12">
+        <v>7</v>
+      </c>
+      <c r="P42" s="12">
+        <v>14</v>
+      </c>
+      <c r="Q42" s="12">
+        <v>2</v>
+      </c>
+      <c r="R42" s="12">
+        <v>19</v>
+      </c>
+      <c r="S42" s="12">
+        <v>4</v>
+      </c>
+      <c r="T42" s="13">
+        <v>17</v>
+      </c>
+      <c r="U42" s="13">
+        <v>6</v>
+      </c>
+      <c r="V42" s="13">
+        <v>9</v>
+      </c>
+      <c r="W42" s="13">
+        <v>2</v>
+      </c>
+      <c r="X42" s="13">
+        <v>10</v>
+      </c>
+      <c r="Y42" s="13">
+        <v>4</v>
+      </c>
+      <c r="Z42" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="15">
+        <v>2</v>
+      </c>
+      <c r="AB42" s="15">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE42" s="15">
+        <v>6</v>
+      </c>
       <c r="AF42" s="4"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="3"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12"/>
-      <c r="Q43" s="12"/>
-      <c r="R43" s="12"/>
-      <c r="S43" s="12"/>
-      <c r="T43" s="13"/>
-      <c r="U43" s="13"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="13"/>
-      <c r="X43" s="13"/>
-      <c r="Y43" s="13"/>
-      <c r="Z43" s="15"/>
-      <c r="AA43" s="15"/>
-      <c r="AB43" s="15"/>
-      <c r="AC43" s="15"/>
-      <c r="AD43" s="15"/>
-      <c r="AE43" s="15"/>
+      <c r="A43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="12">
+        <v>119</v>
+      </c>
+      <c r="C43" s="12">
+        <v>16</v>
+      </c>
+      <c r="D43" s="12">
+        <v>46</v>
+      </c>
+      <c r="E43" s="12">
+        <v>6</v>
+      </c>
+      <c r="F43" s="12">
+        <v>30</v>
+      </c>
+      <c r="G43" s="12">
+        <v>6</v>
+      </c>
+      <c r="H43" s="13">
+        <v>34</v>
+      </c>
+      <c r="I43" s="13">
+        <v>12</v>
+      </c>
+      <c r="J43" s="13">
+        <v>19</v>
+      </c>
+      <c r="K43" s="13">
+        <v>4</v>
+      </c>
+      <c r="L43" s="13">
+        <v>34</v>
+      </c>
+      <c r="M43" s="13">
+        <v>13</v>
+      </c>
+      <c r="N43" s="12">
+        <v>27</v>
+      </c>
+      <c r="O43" s="12">
+        <v>3</v>
+      </c>
+      <c r="P43" s="12">
+        <v>19</v>
+      </c>
+      <c r="Q43" s="12">
+        <v>2</v>
+      </c>
+      <c r="R43" s="12">
+        <v>25</v>
+      </c>
+      <c r="S43" s="12">
+        <v>5</v>
+      </c>
+      <c r="T43" s="13">
+        <v>6</v>
+      </c>
+      <c r="U43" s="13">
+        <v>2</v>
+      </c>
+      <c r="V43" s="13">
+        <v>14</v>
+      </c>
+      <c r="W43" s="13">
+        <v>3</v>
+      </c>
+      <c r="X43" s="13">
+        <v>19</v>
+      </c>
+      <c r="Y43" s="13">
+        <v>7</v>
+      </c>
+      <c r="Z43" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="15">
+        <v>6</v>
+      </c>
+      <c r="AC43" s="15">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE43" s="15">
+        <v>2</v>
+      </c>
       <c r="AF43" s="4"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="3"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="12"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="12"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="13"/>
-      <c r="U44" s="13"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="13"/>
-      <c r="Z44" s="15"/>
-      <c r="AA44" s="15"/>
-      <c r="AB44" s="15"/>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="15"/>
-      <c r="AE44" s="15"/>
+      <c r="A44" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="12">
+        <v>112</v>
+      </c>
+      <c r="C44" s="12">
+        <v>16</v>
+      </c>
+      <c r="D44" s="12">
+        <v>53</v>
+      </c>
+      <c r="E44" s="12">
+        <v>6</v>
+      </c>
+      <c r="F44" s="12">
+        <v>31</v>
+      </c>
+      <c r="G44" s="12">
+        <v>6</v>
+      </c>
+      <c r="H44" s="13">
+        <v>27</v>
+      </c>
+      <c r="I44" s="13">
+        <v>12</v>
+      </c>
+      <c r="J44" s="13">
+        <v>19</v>
+      </c>
+      <c r="K44" s="13">
+        <v>4</v>
+      </c>
+      <c r="L44" s="13">
+        <v>32</v>
+      </c>
+      <c r="M44" s="13">
+        <v>13</v>
+      </c>
+      <c r="N44" s="12">
+        <v>70</v>
+      </c>
+      <c r="O44" s="12">
+        <v>11</v>
+      </c>
+      <c r="P44" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="12">
+        <v>0</v>
+      </c>
+      <c r="R44" s="12">
+        <v>24</v>
+      </c>
+      <c r="S44" s="12">
+        <v>5</v>
+      </c>
+      <c r="T44" s="13">
+        <v>20</v>
+      </c>
+      <c r="U44" s="13">
+        <v>9</v>
+      </c>
+      <c r="V44" s="13">
+        <v>10</v>
+      </c>
+      <c r="W44" s="13">
+        <v>2</v>
+      </c>
+      <c r="X44" s="13">
+        <v>25</v>
+      </c>
+      <c r="Y44" s="13">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="15">
+        <v>2</v>
+      </c>
+      <c r="AB44" s="15">
+        <v>4</v>
+      </c>
+      <c r="AC44" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE44" s="15">
+        <v>6</v>
+      </c>
       <c r="AF44" s="4"/>
     </row>
     <row r="45" spans="1:32">
@@ -5975,7 +6170,7 @@
         <v>6</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:32">
@@ -7033,7 +7228,7 @@
         <v>4</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -7307,7 +7502,9 @@
       <c r="Z25" s="15">
         <v>5</v>
       </c>
-      <c r="AA25" s="15"/>
+      <c r="AA25" s="15">
+        <v>6</v>
+      </c>
       <c r="AB25" s="15">
         <v>4</v>
       </c>
@@ -7323,275 +7520,771 @@
       <c r="AF25" s="4"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="3"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="15"/>
-      <c r="AA26" s="15"/>
-      <c r="AB26" s="15"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
+      <c r="A26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="12">
+        <v>113</v>
+      </c>
+      <c r="C26" s="12">
+        <v>24</v>
+      </c>
+      <c r="D26" s="12">
+        <v>46</v>
+      </c>
+      <c r="E26" s="12">
+        <v>6</v>
+      </c>
+      <c r="F26" s="12">
+        <v>32</v>
+      </c>
+      <c r="G26" s="12">
+        <v>6</v>
+      </c>
+      <c r="H26" s="13">
+        <v>36</v>
+      </c>
+      <c r="I26" s="13">
+        <v>12</v>
+      </c>
+      <c r="J26" s="13">
+        <v>19</v>
+      </c>
+      <c r="K26" s="13">
+        <v>4</v>
+      </c>
+      <c r="L26" s="13">
+        <v>33</v>
+      </c>
+      <c r="M26" s="13">
+        <v>13</v>
+      </c>
+      <c r="N26" s="12">
+        <v>104</v>
+      </c>
+      <c r="O26" s="12">
+        <v>23</v>
+      </c>
+      <c r="P26" s="12">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>5</v>
+      </c>
+      <c r="R26" s="12">
+        <v>26</v>
+      </c>
+      <c r="S26" s="12">
+        <v>5</v>
+      </c>
+      <c r="T26" s="13">
+        <v>34</v>
+      </c>
+      <c r="U26" s="13">
+        <v>11</v>
+      </c>
+      <c r="V26" s="13">
+        <v>15</v>
+      </c>
+      <c r="W26" s="13">
+        <v>3</v>
+      </c>
+      <c r="X26" s="13">
+        <v>23</v>
+      </c>
+      <c r="Y26" s="13">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="15">
+        <v>4</v>
+      </c>
+      <c r="AC26" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="15">
+        <v>6</v>
+      </c>
       <c r="AF26" s="4"/>
     </row>
     <row r="27" spans="1:32">
-      <c r="A27" s="3"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
+      <c r="A27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="12">
+        <v>120</v>
+      </c>
+      <c r="C27" s="12">
+        <v>16</v>
+      </c>
+      <c r="D27" s="12">
+        <v>53</v>
+      </c>
+      <c r="E27" s="12">
+        <v>6</v>
+      </c>
+      <c r="F27" s="12">
+        <v>30</v>
+      </c>
+      <c r="G27" s="12">
+        <v>6</v>
+      </c>
+      <c r="H27" s="13">
+        <v>33</v>
+      </c>
+      <c r="I27" s="13">
+        <v>12</v>
+      </c>
+      <c r="J27" s="13">
+        <v>18</v>
+      </c>
+      <c r="K27" s="13">
+        <v>4</v>
+      </c>
+      <c r="L27" s="13">
+        <v>34</v>
+      </c>
+      <c r="M27" s="13">
+        <v>13</v>
+      </c>
+      <c r="N27" s="12">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12">
+        <v>0</v>
+      </c>
+      <c r="P27" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="12">
+        <v>0</v>
+      </c>
+      <c r="R27" s="12">
+        <v>21</v>
+      </c>
+      <c r="S27" s="12">
+        <v>4</v>
+      </c>
+      <c r="T27" s="13">
+        <v>31</v>
+      </c>
+      <c r="U27" s="13">
+        <v>11</v>
+      </c>
+      <c r="V27" s="13">
+        <v>14</v>
+      </c>
+      <c r="W27" s="13">
+        <v>3</v>
+      </c>
+      <c r="X27" s="13">
+        <v>6</v>
+      </c>
+      <c r="Y27" s="13">
+        <v>2</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="15">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="15">
+        <v>4</v>
+      </c>
+      <c r="AE27" s="15">
+        <v>6</v>
+      </c>
       <c r="AF27" s="4"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="3"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
+      <c r="A28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="12">
+        <v>125</v>
+      </c>
+      <c r="C28" s="12">
+        <v>16</v>
+      </c>
+      <c r="D28" s="12">
+        <v>52</v>
+      </c>
+      <c r="E28" s="12">
+        <v>6</v>
+      </c>
+      <c r="F28" s="12">
+        <v>30</v>
+      </c>
+      <c r="G28" s="12">
+        <v>6</v>
+      </c>
+      <c r="H28" s="13">
+        <v>29</v>
+      </c>
+      <c r="I28" s="13">
+        <v>12</v>
+      </c>
+      <c r="J28" s="13">
+        <v>19</v>
+      </c>
+      <c r="K28" s="13">
+        <v>4</v>
+      </c>
+      <c r="L28" s="13">
+        <v>30</v>
+      </c>
+      <c r="M28" s="13">
+        <v>13</v>
+      </c>
+      <c r="N28" s="12">
+        <v>109</v>
+      </c>
+      <c r="O28" s="12">
+        <v>13</v>
+      </c>
+      <c r="P28" s="12">
+        <v>41</v>
+      </c>
+      <c r="Q28" s="12">
+        <v>5</v>
+      </c>
+      <c r="R28" s="12">
+        <v>20</v>
+      </c>
+      <c r="S28" s="12">
+        <v>4</v>
+      </c>
+      <c r="T28" s="13">
+        <v>25</v>
+      </c>
+      <c r="U28" s="13">
+        <v>11</v>
+      </c>
+      <c r="V28" s="13">
+        <v>14</v>
+      </c>
+      <c r="W28" s="13">
+        <v>3</v>
+      </c>
+      <c r="X28" s="13">
+        <v>26</v>
+      </c>
+      <c r="Y28" s="13">
+        <v>11</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>4</v>
+      </c>
+      <c r="AB28" s="15">
+        <v>6</v>
+      </c>
+      <c r="AC28" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD28" s="15">
+        <v>2</v>
+      </c>
+      <c r="AE28" s="15">
+        <v>1</v>
+      </c>
       <c r="AF28" s="4"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="3"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
+      <c r="A29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="12">
+        <v>111</v>
+      </c>
+      <c r="C29" s="12">
+        <v>16</v>
+      </c>
+      <c r="D29" s="12">
+        <v>49</v>
+      </c>
+      <c r="E29" s="12">
+        <v>6</v>
+      </c>
+      <c r="F29" s="12">
+        <v>30</v>
+      </c>
+      <c r="G29" s="12">
+        <v>6</v>
+      </c>
+      <c r="H29" s="13">
+        <v>30</v>
+      </c>
+      <c r="I29" s="13">
+        <v>12</v>
+      </c>
+      <c r="J29" s="13">
+        <v>20</v>
+      </c>
+      <c r="K29" s="13">
+        <v>4</v>
+      </c>
+      <c r="L29" s="13">
+        <v>30</v>
+      </c>
+      <c r="M29" s="13">
+        <v>13</v>
+      </c>
+      <c r="N29" s="12">
+        <v>57</v>
+      </c>
+      <c r="O29" s="12">
+        <v>9</v>
+      </c>
+      <c r="P29" s="12">
+        <v>22</v>
+      </c>
+      <c r="Q29" s="12">
+        <v>2</v>
+      </c>
+      <c r="R29" s="12">
+        <v>19</v>
+      </c>
+      <c r="S29" s="12">
+        <v>4</v>
+      </c>
+      <c r="T29" s="13">
+        <v>17</v>
+      </c>
+      <c r="U29" s="13">
+        <v>7</v>
+      </c>
+      <c r="V29" s="13">
+        <v>9</v>
+      </c>
+      <c r="W29" s="13">
+        <v>2</v>
+      </c>
+      <c r="X29" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>6</v>
+      </c>
+      <c r="AA29" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="15">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="15">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="15">
+        <v>2</v>
+      </c>
+      <c r="AE29" s="15">
+        <v>3</v>
+      </c>
       <c r="AF29" s="4"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="3"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="13"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
-      <c r="Y30" s="13"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
-      <c r="AE30" s="15"/>
+      <c r="A30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="12">
+        <v>121</v>
+      </c>
+      <c r="C30" s="12">
+        <v>15</v>
+      </c>
+      <c r="D30" s="12">
+        <v>50</v>
+      </c>
+      <c r="E30" s="12">
+        <v>6</v>
+      </c>
+      <c r="F30" s="12">
+        <v>31</v>
+      </c>
+      <c r="G30" s="12">
+        <v>6</v>
+      </c>
+      <c r="H30" s="13">
+        <v>27</v>
+      </c>
+      <c r="I30" s="13">
+        <v>12</v>
+      </c>
+      <c r="J30" s="13">
+        <v>19</v>
+      </c>
+      <c r="K30" s="13">
+        <v>4</v>
+      </c>
+      <c r="L30" s="13">
+        <v>30</v>
+      </c>
+      <c r="M30" s="13">
+        <v>13</v>
+      </c>
+      <c r="N30" s="12">
+        <v>60</v>
+      </c>
+      <c r="O30" s="12">
+        <v>7</v>
+      </c>
+      <c r="P30" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="12">
+        <v>0</v>
+      </c>
+      <c r="R30" s="12">
+        <v>18</v>
+      </c>
+      <c r="S30" s="12">
+        <v>4</v>
+      </c>
+      <c r="T30" s="13">
+        <v>16</v>
+      </c>
+      <c r="U30" s="13">
+        <v>7</v>
+      </c>
+      <c r="V30" s="13">
+        <v>8</v>
+      </c>
+      <c r="W30" s="13">
+        <v>2</v>
+      </c>
+      <c r="X30" s="13">
+        <v>23</v>
+      </c>
+      <c r="Y30" s="13">
+        <v>10</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>6</v>
+      </c>
+      <c r="AB30" s="15">
+        <v>2</v>
+      </c>
+      <c r="AC30" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD30" s="15">
+        <v>4</v>
+      </c>
+      <c r="AE30" s="15">
+        <v>3</v>
+      </c>
       <c r="AF30" s="4"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="3"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="13"/>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
+      <c r="A31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="12">
+        <v>105</v>
+      </c>
+      <c r="C31" s="12">
+        <v>21</v>
+      </c>
+      <c r="D31" s="12">
+        <v>44</v>
+      </c>
+      <c r="E31" s="12">
+        <v>6</v>
+      </c>
+      <c r="F31" s="12">
+        <v>31</v>
+      </c>
+      <c r="G31" s="12">
+        <v>6</v>
+      </c>
+      <c r="H31" s="13">
+        <v>29</v>
+      </c>
+      <c r="I31" s="13">
+        <v>12</v>
+      </c>
+      <c r="J31" s="13">
+        <v>19</v>
+      </c>
+      <c r="K31" s="13">
+        <v>4</v>
+      </c>
+      <c r="L31" s="13">
+        <v>30</v>
+      </c>
+      <c r="M31" s="13">
+        <v>13</v>
+      </c>
+      <c r="N31" s="12">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12">
+        <v>0</v>
+      </c>
+      <c r="P31" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q31" s="12">
+        <v>2</v>
+      </c>
+      <c r="R31" s="12">
+        <v>10</v>
+      </c>
+      <c r="S31" s="12">
+        <v>2</v>
+      </c>
+      <c r="T31" s="13">
+        <v>24</v>
+      </c>
+      <c r="U31" s="13">
+        <v>10</v>
+      </c>
+      <c r="V31" s="13">
+        <v>14</v>
+      </c>
+      <c r="W31" s="13">
+        <v>3</v>
+      </c>
+      <c r="X31" s="13">
+        <v>26</v>
+      </c>
+      <c r="Y31" s="13">
+        <v>11</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA31" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB31" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="15">
+        <v>6</v>
+      </c>
+      <c r="AD31" s="15">
+        <v>4</v>
+      </c>
+      <c r="AE31" s="15">
+        <v>2</v>
+      </c>
       <c r="AF31" s="4"/>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="13"/>
-      <c r="U32" s="13"/>
-      <c r="V32" s="13"/>
-      <c r="W32" s="13"/>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
-      <c r="AE32" s="15"/>
+      <c r="A32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="12">
+        <v>120</v>
+      </c>
+      <c r="C32" s="12">
+        <v>13</v>
+      </c>
+      <c r="D32" s="12">
+        <v>44</v>
+      </c>
+      <c r="E32" s="12">
+        <v>6</v>
+      </c>
+      <c r="F32" s="12">
+        <v>31</v>
+      </c>
+      <c r="G32" s="12">
+        <v>6</v>
+      </c>
+      <c r="H32" s="13">
+        <v>27</v>
+      </c>
+      <c r="I32" s="13">
+        <v>12</v>
+      </c>
+      <c r="J32" s="13">
+        <v>19</v>
+      </c>
+      <c r="K32" s="13">
+        <v>4</v>
+      </c>
+      <c r="L32" s="13">
+        <v>32</v>
+      </c>
+      <c r="M32" s="13">
+        <v>13</v>
+      </c>
+      <c r="N32" s="12">
+        <v>73</v>
+      </c>
+      <c r="O32" s="12">
+        <v>8</v>
+      </c>
+      <c r="P32" s="12">
+        <v>28</v>
+      </c>
+      <c r="Q32" s="12">
+        <v>4</v>
+      </c>
+      <c r="R32" s="12">
+        <v>26</v>
+      </c>
+      <c r="S32" s="12">
+        <v>5</v>
+      </c>
+      <c r="T32" s="13">
+        <v>20</v>
+      </c>
+      <c r="U32" s="13">
+        <v>9</v>
+      </c>
+      <c r="V32" s="13">
+        <v>14</v>
+      </c>
+      <c r="W32" s="13">
+        <v>3</v>
+      </c>
+      <c r="X32" s="13">
+        <v>22</v>
+      </c>
+      <c r="Y32" s="13">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="15">
+        <v>6</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="15">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="15">
+        <v>5</v>
+      </c>
       <c r="AF32" s="4"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="3"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="13"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
-      <c r="AE33" s="15"/>
+      <c r="A33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="12">
+        <v>112</v>
+      </c>
+      <c r="C33" s="12">
+        <v>15</v>
+      </c>
+      <c r="D33" s="12">
+        <v>45</v>
+      </c>
+      <c r="E33" s="12">
+        <v>6</v>
+      </c>
+      <c r="F33" s="12">
+        <v>30</v>
+      </c>
+      <c r="G33" s="12">
+        <v>6</v>
+      </c>
+      <c r="H33" s="13">
+        <v>28</v>
+      </c>
+      <c r="I33" s="13">
+        <v>12</v>
+      </c>
+      <c r="J33" s="13">
+        <v>19</v>
+      </c>
+      <c r="K33" s="13">
+        <v>4</v>
+      </c>
+      <c r="L33" s="13">
+        <v>32</v>
+      </c>
+      <c r="M33" s="13">
+        <v>13</v>
+      </c>
+      <c r="N33" s="12">
+        <v>81</v>
+      </c>
+      <c r="O33" s="12">
+        <v>11</v>
+      </c>
+      <c r="P33" s="12">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="12">
+        <v>3</v>
+      </c>
+      <c r="R33" s="12">
+        <v>25</v>
+      </c>
+      <c r="S33" s="12">
+        <v>5</v>
+      </c>
+      <c r="T33" s="13">
+        <v>22</v>
+      </c>
+      <c r="U33" s="13">
+        <v>10</v>
+      </c>
+      <c r="V33" s="13">
+        <v>15</v>
+      </c>
+      <c r="W33" s="13">
+        <v>3</v>
+      </c>
+      <c r="X33" s="13">
+        <v>26</v>
+      </c>
+      <c r="Y33" s="13">
+        <v>11</v>
+      </c>
+      <c r="Z33" s="15">
+        <v>4</v>
+      </c>
+      <c r="AA33" s="15">
+        <v>2</v>
+      </c>
+      <c r="AB33" s="15">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="15">
+        <v>6</v>
+      </c>
+      <c r="AE33" s="15">
+        <v>1</v>
+      </c>
       <c r="AF33" s="4"/>
     </row>
     <row r="34" spans="1:32">
@@ -8181,15 +8874,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Status xmlns="39ce33b2-671c-4713-8621-0a4725eb6492" xsi:nil="true"/>
@@ -8201,14 +8885,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{857B8C61-14C8-41C7-8625-EFF33301E73B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4645D51E-65B6-47C9-8112-61C795F1F2D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47106059-789E-4A5C-86F4-BF90B28AB994}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47106059-789E-4A5C-86F4-BF90B28AB994}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4645D51E-65B6-47C9-8112-61C795F1F2D5}"/>
 </file>